--- a/statistics_tables/variety_tkw_results.xlsx
+++ b/statistics_tables/variety_tkw_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">location</t>
   </si>
@@ -33,6 +33,12 @@
   </si>
   <si>
     <t xml:space="preserve">groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSD</t>
   </si>
   <si>
     <t xml:space="preserve">mean_group_se</t>
@@ -512,19 +518,25 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>2022</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>49.4217084136159</v>
@@ -533,33 +545,37 @@
         <v>0.887682234024736</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.109338036455332</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="n">
         <v>4.98303720528282</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>48.7958306572468</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.102120143015595</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="n">
         <v>2022</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>47.3740366088632</v>
@@ -568,33 +584,37 @@
         <v>0.789681085670395</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.109338036455332</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.98303720528282</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>48.7958306572468</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.102120143015595</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
         <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>49.5917469492614</v>
@@ -603,33 +623,37 @@
         <v>0.781031844855827</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.109338036455332</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.98303720528282</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>48.7958306572468</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.102120143015595</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>42.3305555555556</v>
@@ -638,33 +662,39 @@
         <v>0.503776522708682</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.00000000117249547273641</v>
       </c>
       <c r="I5" t="n">
+        <v>1.19772486270719</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.08794748909309</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>42.6509259259259</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.0724004795219708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>40.6861111111111</v>
@@ -673,33 +703,39 @@
         <v>0.323378808235048</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.00000000117249547273641</v>
       </c>
       <c r="I6" t="n">
+        <v>1.19772486270719</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.08794748909309</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>42.6509259259259</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.0724004795219708</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>44.9361111111111</v>
@@ -708,33 +744,39 @@
         <v>0.434689321235837</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.00000000117249547273641</v>
       </c>
       <c r="I7" t="n">
+        <v>1.19772486270719</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.08794748909309</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>42.6509259259259</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0724004795219708</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
         <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>50.9818055555556</v>
@@ -743,33 +785,39 @@
         <v>0.256340404322079</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0000000000000000000000000000228182591738912</v>
       </c>
       <c r="I8" t="n">
+        <v>1.13629703957932</v>
+      </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" t="n">
         <v>4.51363976155715</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>51.3180092592593</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0879543035029708</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" t="n">
         <v>2022</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>46.8416666666667</v>
@@ -778,33 +826,39 @@
         <v>0.608046246674739</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0000000000000000000000000000228182591738912</v>
       </c>
       <c r="I9" t="n">
+        <v>1.13629703957932</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.51363976155715</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>51.3180092592593</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.0879543035029708</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" t="n">
         <v>2022</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>56.1305555555556</v>
@@ -813,33 +867,39 @@
         <v>0.239139311342316</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0000000000000000000000000000228182591738912</v>
       </c>
       <c r="I10" t="n">
+        <v>1.13629703957932</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.51363976155715</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>51.3180092592593</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.0879543035029708</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>50.0829166666667</v>
@@ -848,33 +908,39 @@
         <v>0.33070837720561</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.000000000205944798257908</v>
       </c>
       <c r="I11" t="n">
+        <v>2.06585489713149</v>
+      </c>
+      <c r="J11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" t="n">
         <v>5.41510103003439</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>50.5262969653179</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.107173914481629</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>46.8833333333333</v>
@@ -883,33 +949,39 @@
         <v>0.848167960305557</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" t="s">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.000000000205944798257908</v>
       </c>
       <c r="I12" t="n">
+        <v>2.06585489713149</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="n">
         <v>5.41510103003439</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>50.5262969653179</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.107173914481629</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>54.6126408959538</v>
@@ -918,33 +990,39 @@
         <v>0.894154857677896</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.000000000205944798257908</v>
       </c>
       <c r="I13" t="n">
+        <v>2.06585489713149</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" t="n">
         <v>5.41510103003439</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>50.5262969653179</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.107173914481629</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B14" t="n">
         <v>2024</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>49.6500508188825</v>
@@ -953,33 +1031,39 @@
         <v>0.693380674864465</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" t="s">
-        <v>32</v>
+        <v>22</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.00000263610314141582</v>
       </c>
       <c r="I14" t="n">
+        <v>1.82357340720304</v>
+      </c>
+      <c r="J14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.36831250048021</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>51.1865755191608</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.0853409796645804</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="n">
         <v>2024</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>49.860908879255</v>
@@ -988,33 +1072,39 @@
         <v>0.668888643427421</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" t="s">
-        <v>33</v>
+        <v>22</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.00000263610314141582</v>
       </c>
       <c r="I15" t="n">
+        <v>1.82357340720304</v>
+      </c>
+      <c r="J15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.36831250048021</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>51.1865755191608</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.0853409796645804</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" t="n">
         <v>2024</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>54.0487668593449</v>
@@ -1023,33 +1113,39 @@
         <v>0.583569209789068</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" t="s">
-        <v>34</v>
+        <v>16</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.00000263610314141582</v>
       </c>
       <c r="I16" t="n">
+        <v>1.82357340720304</v>
+      </c>
+      <c r="J16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.36831250048021</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>51.1865755191608</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.0853409796645804</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" t="n">
         <v>2022</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>47.1763680154143</v>
@@ -1058,33 +1154,37 @@
         <v>0.309015843273658</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.526847534294903</v>
+      </c>
+      <c r="I17"/>
+      <c r="J17" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.16210059722546</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>46.920502569043</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0460800818159173</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" t="n">
         <v>2022</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>46.6049951830443</v>
@@ -1093,33 +1193,37 @@
         <v>0.475868071173889</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.526847534294903</v>
+      </c>
+      <c r="I18"/>
+      <c r="J18" t="s">
+        <v>39</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.16210059722546</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>46.920502569043</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.0460800818159173</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" t="n">
         <v>2022</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>46.9801445086705</v>
@@ -1128,33 +1232,37 @@
         <v>0.26498911813837</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" t="s">
-        <v>38</v>
-      </c>
-      <c r="I19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.526847534294903</v>
+      </c>
+      <c r="I19"/>
+      <c r="J19" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.16210059722546</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>46.920502569043</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.0460800818159173</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>51.5555555555556</v>
@@ -1163,33 +1271,39 @@
         <v>1.13752337805695</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0272523298106954</v>
       </c>
       <c r="I20" t="n">
+        <v>2.02989960998716</v>
+      </c>
+      <c r="J20" t="s">
+        <v>42</v>
+      </c>
+      <c r="K20" t="n">
         <v>4.4527902235963</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>51.6435185185185</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.086221666364572</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>50.2916666666667</v>
@@ -1198,33 +1312,39 @@
         <v>0.344673183138177</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" t="s">
-        <v>41</v>
+        <v>22</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0272523298106954</v>
       </c>
       <c r="I21" t="n">
+        <v>2.02989960998716</v>
+      </c>
+      <c r="J21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K21" t="n">
         <v>4.4527902235963</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>51.6435185185185</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.086221666364572</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
         <v>53.0833333333333</v>
@@ -1233,33 +1353,39 @@
         <v>0.399155855306416</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0272523298106954</v>
       </c>
       <c r="I22" t="n">
+        <v>2.02989960998716</v>
+      </c>
+      <c r="J22" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.4527902235963</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>51.6435185185185</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.086221666364572</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" t="n">
         <v>2024</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>43.9803211303789</v>
@@ -1268,33 +1394,39 @@
         <v>0.45021370322119</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" t="s">
-        <v>43</v>
+        <v>22</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.00000000258188471520863</v>
       </c>
       <c r="I23" t="n">
+        <v>1.42189545596379</v>
+      </c>
+      <c r="J23" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.63844237942205</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>45.5785174480839</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.0798280107194449</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24" t="n">
         <v>2024</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
         <v>44.3139049454078</v>
@@ -1303,33 +1435,39 @@
         <v>0.57407545228224</v>
       </c>
       <c r="G24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" t="s">
-        <v>44</v>
+        <v>22</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00000000258188471520863</v>
       </c>
       <c r="I24" t="n">
+        <v>1.42189545596379</v>
+      </c>
+      <c r="J24" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.63844237942205</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>45.5785174480839</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.0798280107194449</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" t="n">
         <v>2024</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>48.441326268465</v>
@@ -1338,18 +1476,24 @@
         <v>0.488992655598817</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
-        <v>45</v>
+        <v>16</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.00000000258188471520863</v>
       </c>
       <c r="I25" t="n">
+        <v>1.42189545596379</v>
+      </c>
+      <c r="J25" t="s">
+        <v>47</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.63844237942205</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>45.5785174480839</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0798280107194449</v>
       </c>
     </row>
